--- a/datos/datos_bonbonite.xlsx
+++ b/datos/datos_bonbonite.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Registro" sheetId="1" r:id="rId1"/>
     <sheet name="Login" sheetId="2" r:id="rId2"/>
-    <sheet name="Zapatos" sheetId="3" r:id="rId3"/>
+    <sheet name="Producto" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>cedula</t>
   </si>
@@ -57,6 +57,21 @@
   </si>
   <si>
     <t>mocasin en cuero miel</t>
+  </si>
+  <si>
+    <t>producto</t>
+  </si>
+  <si>
+    <t>img_producto</t>
+  </si>
+  <si>
+    <t>talla_producto</t>
+  </si>
+  <si>
+    <t>Zapatos</t>
+  </si>
+  <si>
+    <t>mocasin-en-cuero-miel-199052-A-600x600.png</t>
   </si>
 </sst>
 </file>
@@ -489,24 +504,45 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="23.6640625" customWidth="1"/>
+    <col min="3" max="3" width="39.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="B4" s="4"/>
+      <c r="D4" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
